--- a/eduservices/DRILL2_EXCEL.xlsx
+++ b/eduservices/DRILL2_EXCEL.xlsx
@@ -16,12 +16,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0&quot; €&quot;"/>
     <numFmt numFmtId="165" formatCode="&quot;▲ &quot;#,##0;&quot;▼ &quot;#,##0;&quot;—&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="+#,##0&quot; €&quot;;-#,##0&quot; €&quot;;&quot;0 €&quot;"/>
+    <numFmt numFmtId="168" formatCode="+0.00%;-0.00%;&quot;0,00 %&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,8 +99,26 @@
       <color rgb="002A78D6"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00202733"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002A78D6"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="0069778B"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -125,8 +145,13 @@
         <fgColor rgb="00EAF2FC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -156,11 +181,21 @@
         <color rgb="00526071"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00E9EDF3"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00526071"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -215,6 +250,26 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="14" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -374,12 +429,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Drill par compte'!$K$35:$K$53</f>
+              <f>'Drill par compte'!$K$35:$K$47</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Drill par compte'!$L$35:$L$53</f>
+              <f>'Drill par compte'!$L$35:$L$47</f>
             </numRef>
           </val>
         </ser>
@@ -400,12 +455,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Drill par compte'!$K$35:$K$53</f>
+              <f>'Drill par compte'!$K$35:$K$47</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Drill par compte'!$M$35:$M$53</f>
+              <f>'Drill par compte'!$M$35:$M$47</f>
             </numRef>
           </val>
         </ser>
@@ -421,7 +476,7 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <numFmt formatCode="#,##0,,&quot; M€&quot;" sourceLinked="0"/>
+        <numFmt formatCode="#,##0,&quot; k€&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -458,7 +513,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8280000" cy="4860000"/>
+    <ext cx="7560000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -765,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -841,7 +896,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="5">
-        <f>"Sur "&amp;TEXT(G34,"#,##0 €")&amp;" de chiffre d'affaires, "&amp;TEXT(-SUM(G35:G53),"#,##0 €")&amp;" partent en charges. Il reste "&amp;TEXT(SUM(G34:G53),"#,##0 €")&amp;" d'EBITDA, soit "&amp;TEXT(SUM(G34:G53)/G34,"0.0%")&amp;" du chiffre d'affaires."</f>
+        <f>"Sur "&amp;TEXT(G34,"#,##0 €")&amp;" de chiffre d'affaires, "&amp;TEXT(-SUM(G35:G47),"#,##0 €")&amp;" partent en charges. Il reste "&amp;TEXT(SUM(G34:G47),"#,##0 €")&amp;" d'EBITDA, soit "&amp;TEXT(SUM(G34:G47)/G34,"0.0%")&amp;" du chiffre d'affaires."</f>
         <v/>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1270,10 +1325,15 @@
         <v/>
       </c>
       <c r="I34" s="17">
-        <f>IF(OR(B34="",B34=1),"",-G34/SUM(G35:G53))</f>
+        <f>IF(OR(B34="",B34=1),"",-G34/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J34" s="4" t="n"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
       <c r="A35" s="4" t="n"/>
@@ -1306,13 +1366,14 @@
         <v/>
       </c>
       <c r="I35" s="17">
-        <f>IF(OR(B35="",B35=1),"",-G35/SUM(G35:G53))</f>
+        <f>IF(OR(B35="",B35=1),"",-G35/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J35" s="4" t="n"/>
-      <c r="K35">
-        <f>E35</f>
-        <v/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Vacataires</t>
+        </is>
       </c>
       <c r="L35">
         <f>-F35</f>
@@ -1354,13 +1415,14 @@
         <v/>
       </c>
       <c r="I36" s="17">
-        <f>IF(OR(B36="",B36=1),"",-G36/SUM(G35:G53))</f>
+        <f>IF(OR(B36="",B36=1),"",-G36/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J36" s="4" t="n"/>
-      <c r="K36">
-        <f>E36</f>
-        <v/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Achats d'études</t>
+        </is>
       </c>
       <c r="L36">
         <f>-F36</f>
@@ -1402,13 +1464,14 @@
         <v/>
       </c>
       <c r="I37" s="17">
-        <f>IF(OR(B37="",B37=1),"",-G37/SUM(G35:G53))</f>
+        <f>IF(OR(B37="",B37=1),"",-G37/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J37" s="4" t="n"/>
-      <c r="K37">
-        <f>E37</f>
-        <v/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Fournitures</t>
+        </is>
       </c>
       <c r="L37">
         <f>-F37</f>
@@ -1450,13 +1513,14 @@
         <v/>
       </c>
       <c r="I38" s="17">
-        <f>IF(OR(B38="",B38=1),"",-G38/SUM(G35:G53))</f>
+        <f>IF(OR(B38="",B38=1),"",-G38/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J38" s="4" t="n"/>
-      <c r="K38">
-        <f>E38</f>
-        <v/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
       </c>
       <c r="L38">
         <f>-F38</f>
@@ -1498,13 +1562,14 @@
         <v/>
       </c>
       <c r="I39" s="17">
-        <f>IF(OR(B39="",B39=1),"",-G39/SUM(G35:G53))</f>
+        <f>IF(OR(B39="",B39=1),"",-G39/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J39" s="4" t="n"/>
-      <c r="K39">
-        <f>E39</f>
-        <v/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Salaires</t>
+        </is>
       </c>
       <c r="L39">
         <f>-F39</f>
@@ -1546,13 +1611,14 @@
         <v/>
       </c>
       <c r="I40" s="17">
-        <f>IF(OR(B40="",B40=1),"",-G40/SUM(G35:G53))</f>
+        <f>IF(OR(B40="",B40=1),"",-G40/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J40" s="4" t="n"/>
-      <c r="K40">
-        <f>E40</f>
-        <v/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Primes</t>
+        </is>
       </c>
       <c r="L40">
         <f>-F40</f>
@@ -1594,13 +1660,14 @@
         <v/>
       </c>
       <c r="I41" s="17">
-        <f>IF(OR(B41="",B41=1),"",-G41/SUM(G35:G53))</f>
+        <f>IF(OR(B41="",B41=1),"",-G41/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J41" s="4" t="n"/>
-      <c r="K41">
-        <f>E41</f>
-        <v/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Charges sociales</t>
+        </is>
       </c>
       <c r="L41">
         <f>-F41</f>
@@ -1642,13 +1709,14 @@
         <v/>
       </c>
       <c r="I42" s="17">
-        <f>IF(OR(B42="",B42=1),"",-G42/SUM(G35:G53))</f>
+        <f>IF(OR(B42="",B42=1),"",-G42/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J42" s="4" t="n"/>
-      <c r="K42">
-        <f>E42</f>
-        <v/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Loyers</t>
+        </is>
       </c>
       <c r="L42">
         <f>-F42</f>
@@ -1690,13 +1758,14 @@
         <v/>
       </c>
       <c r="I43" s="17">
-        <f>IF(OR(B43="",B43=1),"",-G43/SUM(G35:G53))</f>
+        <f>IF(OR(B43="",B43=1),"",-G43/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J43" s="4" t="n"/>
-      <c r="K43">
-        <f>E43</f>
-        <v/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Entretien</t>
+        </is>
       </c>
       <c r="L43">
         <f>-F43</f>
@@ -1738,13 +1807,14 @@
         <v/>
       </c>
       <c r="I44" s="17">
-        <f>IF(OR(B44="",B44=1),"",-G44/SUM(G35:G53))</f>
+        <f>IF(OR(B44="",B44=1),"",-G44/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
-      <c r="K44">
-        <f>E44</f>
-        <v/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Assurances</t>
+        </is>
       </c>
       <c r="L44">
         <f>-F44</f>
@@ -1786,13 +1856,14 @@
         <v/>
       </c>
       <c r="I45" s="17">
-        <f>IF(OR(B45="",B45=1),"",-G45/SUM(G35:G53))</f>
+        <f>IF(OR(B45="",B45=1),"",-G45/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J45" s="4" t="n"/>
-      <c r="K45">
-        <f>E45</f>
-        <v/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Déplacements</t>
+        </is>
       </c>
       <c r="L45">
         <f>-F45</f>
@@ -1834,13 +1905,14 @@
         <v/>
       </c>
       <c r="I46" s="17">
-        <f>IF(OR(B46="",B46=1),"",-G46/SUM(G35:G53))</f>
+        <f>IF(OR(B46="",B46=1),"",-G46/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J46" s="4" t="n"/>
-      <c r="K46">
-        <f>E46</f>
-        <v/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
       </c>
       <c r="L46">
         <f>-F46</f>
@@ -1878,13 +1950,14 @@
         <v/>
       </c>
       <c r="I47" s="17">
-        <f>IF(OR(B47="",B47=1),"",-G47/SUM(G35:G53))</f>
+        <f>IF(OR(B47="",B47=1),"",-G47/SUM(G35:G47))</f>
         <v/>
       </c>
       <c r="J47" s="4" t="n"/>
-      <c r="K47">
-        <f>E47</f>
-        <v/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Siège</t>
+        </is>
       </c>
       <c r="L47">
         <f>-F47</f>
@@ -1895,191 +1968,159 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="15.5" customHeight="1">
+    <row r="48">
       <c r="A48" s="4" t="n"/>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="13" t="n"/>
-      <c r="E48" s="14" t="n"/>
-      <c r="F48" s="15" t="n"/>
-      <c r="G48" s="15" t="n"/>
-      <c r="H48" s="16" t="n"/>
-      <c r="I48" s="17" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
-      <c r="K48">
-        <f>IF(B48="","",E48)</f>
-        <v/>
-      </c>
-      <c r="L48">
-        <f>IF(B48="",NA(),-F48)</f>
-        <v/>
-      </c>
-      <c r="M48">
-        <f>IF(B48="",NA(),-G48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="15.5" customHeight="1">
+    </row>
+    <row r="49">
       <c r="A49" s="4" t="n"/>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="14" t="n"/>
-      <c r="F49" s="15" t="n"/>
-      <c r="G49" s="15" t="n"/>
-      <c r="H49" s="16" t="n"/>
-      <c r="I49" s="17" t="n"/>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>Contrôle</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="n"/>
+      <c r="D49" s="19" t="n"/>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>la somme des quatorze lignes doit valoir l'EBITDA</t>
+        </is>
+      </c>
+      <c r="F49" s="20">
+        <f>SUM(F34:F47)</f>
+        <v/>
+      </c>
+      <c r="G49" s="20">
+        <f>SUM(G34:G47)</f>
+        <v/>
+      </c>
+      <c r="H49" s="19" t="n"/>
+      <c r="I49" s="19" t="n"/>
       <c r="J49" s="4" t="n"/>
-      <c r="K49">
-        <f>IF(B49="","",E49)</f>
-        <v/>
-      </c>
-      <c r="L49">
-        <f>IF(B49="",NA(),-F49)</f>
-        <v/>
-      </c>
-      <c r="M49">
-        <f>IF(B49="",NA(),-G49)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="15.5" customHeight="1">
+    </row>
+    <row r="50">
       <c r="A50" s="4" t="n"/>
-      <c r="B50" s="11" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="14" t="n"/>
-      <c r="F50" s="15" t="n"/>
-      <c r="G50" s="15" t="n"/>
-      <c r="H50" s="16" t="n"/>
-      <c r="I50" s="17" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
-      <c r="K50">
-        <f>IF(B50="","",E50)</f>
-        <v/>
-      </c>
-      <c r="L50">
-        <f>IF(B50="",NA(),-F50)</f>
-        <v/>
-      </c>
-      <c r="M50">
-        <f>IF(B50="",NA(),-G50)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="15.5" customHeight="1">
+    </row>
+    <row r="51" ht="20" customHeight="1">
       <c r="A51" s="4" t="n"/>
-      <c r="B51" s="11" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="13" t="n"/>
-      <c r="E51" s="14" t="n"/>
-      <c r="F51" s="15" t="n"/>
-      <c r="G51" s="15" t="n"/>
-      <c r="H51" s="16" t="n"/>
-      <c r="I51" s="17" t="n"/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>POURQUOI LE CHIFFRE D'AFFAIRES VIENT DU SOCLE CRM</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
       <c r="J51" s="4" t="n"/>
-      <c r="K51">
-        <f>IF(B51="","",E51)</f>
-        <v/>
-      </c>
-      <c r="L51">
-        <f>IF(B51="",NA(),-F51)</f>
-        <v/>
-      </c>
-      <c r="M51">
-        <f>IF(B51="",NA(),-G51)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="15.5" customHeight="1">
+    </row>
+    <row r="52">
       <c r="A52" s="4" t="n"/>
-      <c r="B52" s="11" t="n"/>
-      <c r="C52" s="12" t="n"/>
-      <c r="D52" s="13" t="n"/>
-      <c r="E52" s="14" t="n"/>
-      <c r="F52" s="15" t="n"/>
-      <c r="G52" s="15" t="n"/>
-      <c r="H52" s="16" t="n"/>
-      <c r="I52" s="17" t="n"/>
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires en comptabilité  ·  706 + 7062 + 708</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="22" t="n"/>
+      <c r="F52" s="23" t="n">
+        <v>21775820</v>
+      </c>
+      <c r="G52" s="23" t="n">
+        <v>23098985</v>
+      </c>
+      <c r="H52" s="22" t="n"/>
+      <c r="I52" s="22" t="n"/>
       <c r="J52" s="4" t="n"/>
-      <c r="K52">
-        <f>IF(B52="","",E52)</f>
-        <v/>
-      </c>
-      <c r="L52">
-        <f>IF(B52="",NA(),-F52)</f>
-        <v/>
-      </c>
-      <c r="M52">
-        <f>IF(B52="",NA(),-G52)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="15.5" customHeight="1">
+    </row>
+    <row r="53">
       <c r="A53" s="4" t="n"/>
-      <c r="B53" s="11" t="n"/>
-      <c r="C53" s="12" t="n"/>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="14" t="n"/>
-      <c r="F53" s="15" t="n"/>
-      <c r="G53" s="15" t="n"/>
-      <c r="H53" s="16" t="n"/>
-      <c r="I53" s="17" t="n"/>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires du socle CRM  ·  effectifs × droits de scolarité</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="22" t="n"/>
+      <c r="F53" s="23" t="n">
+        <v>21758770</v>
+      </c>
+      <c r="G53" s="23" t="n">
+        <v>23098985</v>
+      </c>
+      <c r="H53" s="22" t="n"/>
+      <c r="I53" s="22" t="n"/>
       <c r="J53" s="4" t="n"/>
-      <c r="K53">
-        <f>IF(B53="","",E53)</f>
-        <v/>
-      </c>
-      <c r="L53">
-        <f>IF(B53="",NA(),-F53)</f>
-        <v/>
-      </c>
-      <c r="M53">
-        <f>IF(B53="",NA(),-G53)</f>
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n"/>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>Écart</t>
+        </is>
+      </c>
+      <c r="C54" s="25" t="n"/>
+      <c r="D54" s="25" t="n"/>
+      <c r="E54" s="25" t="n"/>
+      <c r="F54" s="26">
+        <f>F52-F53</f>
+        <v/>
+      </c>
+      <c r="G54" s="26">
+        <f>G52-G53</f>
+        <v/>
+      </c>
+      <c r="H54" s="27">
+        <f>F54/F53</f>
+        <v/>
+      </c>
+      <c r="I54" s="27">
+        <f>G54/G53</f>
+        <v/>
+      </c>
       <c r="J54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
-      <c r="B55" s="18" t="inlineStr">
-        <is>
-          <t>Contrôle</t>
-        </is>
-      </c>
-      <c r="C55" s="19" t="n"/>
-      <c r="D55" s="19" t="n"/>
-      <c r="E55" s="18" t="inlineStr">
-        <is>
-          <t>la somme des quatorze lignes doit valoir l'EBITDA</t>
-        </is>
-      </c>
-      <c r="F55" s="20">
-        <f>SUM(F34:F53)</f>
-        <v/>
-      </c>
-      <c r="G55" s="20">
-        <f>SUM(G34:G53)</f>
-        <v/>
-      </c>
-      <c r="H55" s="19" t="n"/>
-      <c r="I55" s="19" t="n"/>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n"/>
-      <c r="B56" s="4" t="n"/>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>Les deux disent la même chose. Le modèle prend le CRM pour deux raisons qui ne tiennent pas à l'exactitude :</t>
+        </is>
+      </c>
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="n"/>
@@ -2091,7 +2132,11 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="n"/>
-      <c r="B57" s="4" t="n"/>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>le GRAIN — 180 lignes campus × programme × année × modalité contre 105 au grain campus × compte, sans quoi aucune marge par programme n'est calculable ;</t>
+        </is>
+      </c>
       <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="n"/>
@@ -2103,7 +2148,11 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="n"/>
-      <c r="B58" s="4" t="n"/>
+      <c r="B58" s="28" t="inlineStr">
+        <is>
+          <t>le PILOTAGE — le CRM donne le CA comme un produit d'inducteurs, effectifs × droits de scolarité, donc il se simule. Un montant comptable est un constat.</t>
+        </is>
+      </c>
       <c r="C58" s="4" t="n"/>
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
@@ -2185,80 +2234,8 @@
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="4" t="n"/>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="n"/>
-      <c r="B65" s="4" t="n"/>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="4" t="n"/>
-      <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n"/>
-      <c r="J65" s="4" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="n"/>
-      <c r="B66" s="4" t="n"/>
-      <c r="C66" s="4" t="n"/>
-      <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="n"/>
-      <c r="F66" s="4" t="n"/>
-      <c r="G66" s="4" t="n"/>
-      <c r="H66" s="4" t="n"/>
-      <c r="I66" s="4" t="n"/>
-      <c r="J66" s="4" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="n"/>
-      <c r="B67" s="4" t="n"/>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n"/>
-      <c r="F67" s="4" t="n"/>
-      <c r="G67" s="4" t="n"/>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="n"/>
-      <c r="J67" s="4" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="n"/>
-      <c r="B68" s="4" t="n"/>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n"/>
-      <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="n"/>
-      <c r="J68" s="4" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="n"/>
-      <c r="B69" s="4" t="n"/>
-      <c r="C69" s="4" t="n"/>
-      <c r="D69" s="4" t="n"/>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="n"/>
-      <c r="G69" s="4" t="n"/>
-      <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="n"/>
-      <c r="J69" s="4" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="n"/>
-      <c r="B70" s="4" t="n"/>
-      <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="n"/>
-      <c r="F70" s="4" t="n"/>
-      <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="n"/>
-      <c r="J70" s="4" t="n"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B34:I53">
+  <conditionalFormatting sqref="B34:I47">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$B34=1</formula>
     </cfRule>
@@ -2269,7 +2246,7 @@
       <formula>$B34&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H53">
+  <conditionalFormatting sqref="H34:H47">
     <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -2277,7 +2254,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I34:I53">
+  <conditionalFormatting sqref="I34:I47">
     <cfRule type="dataBar" priority="6">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>

--- a/eduservices/DRILL2_EXCEL.xlsx
+++ b/eduservices/DRILL2_EXCEL.xlsx
@@ -2022,7 +2022,7 @@
       <c r="A51" s="4" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>POURQUOI LE CHIFFRE D'AFFAIRES VIENT DU SOCLE CRM</t>
+          <t>RAPPROCHEMENT DU CHIFFRE D'AFFAIRES  ·  gestion contre socle CRM</t>
         </is>
       </c>
       <c r="C51" s="4" t="n"/>
@@ -2038,7 +2038,7 @@
       <c r="A52" s="4" t="n"/>
       <c r="B52" s="21" t="inlineStr">
         <is>
-          <t>Chiffre d'affaires en comptabilité  ·  706 + 7062 + 708</t>
+          <t>Chiffre d'affaires en gestion  ·  706 initiaux + 7062 alternants + 708 inscription</t>
         </is>
       </c>
       <c r="C52" s="22" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="A56" s="4" t="n"/>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>Les deux disent la même chose. Le modèle prend le CRM pour deux raisons qui ne tiennent pas à l'exactitude :</t>
+          <t>L'écart est normal et n'est pas corrigé : cette table porte l'ESTIMÉ, pas un grand livre clôturé. Sept centièmes de pour cent entre un estimé et un modèle piloté par les inducteurs, c'est le fonctionnement des deux chaînes.</t>
         </is>
       </c>
       <c r="C56" s="4" t="n"/>
@@ -2134,7 +2134,7 @@
       <c r="A57" s="4" t="n"/>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>le GRAIN — 180 lignes campus × programme × année × modalité contre 105 au grain campus × compte, sans quoi aucune marge par programme n'est calculable ;</t>
+          <t>2026 tombe au centime parce que l'exercice est construit depuis le socle, donc aligné par construction. Les exercices passés portent un estimé établi séparément.</t>
         </is>
       </c>
       <c r="C57" s="4" t="n"/>
@@ -2150,7 +2150,7 @@
       <c r="A58" s="4" t="n"/>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>le PILOTAGE — le CRM donne le CA comme un produit d'inducteurs, effectifs × droits de scolarité, donc il se simule. Un montant comptable est un constat.</t>
+          <t>Le modèle prend le CRM pour deux raisons qui ne tiennent pas à l'exactitude. Le GRAIN — 180 lignes campus × programme × année × modalité contre 105 au grain campus × compte, sans quoi aucune marge par programme n'est calculable.</t>
         </is>
       </c>
       <c r="C58" s="4" t="n"/>
@@ -2164,7 +2164,11 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="n"/>
-      <c r="B59" s="4" t="n"/>
+      <c r="B59" s="28" t="inlineStr">
+        <is>
+          <t>Et le PILOTAGE — le CRM donne le CA comme un produit d'inducteurs, effectifs × droits de scolarité, donc il se simule. Un montant déjà posé est un constat.</t>
+        </is>
+      </c>
       <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="n"/>

--- a/eduservices/DRILL2_EXCEL.xlsx
+++ b/eduservices/DRILL2_EXCEL.xlsx
@@ -43,6 +43,12 @@
       <sz val="8"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0069778B"/>
+      <sz val="8"/>
+    </font>
+    <font>
       <name val="Fira Sans Medium"/>
       <b val="1"/>
       <color rgb="00202733"/>
@@ -71,11 +77,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0069778B"/>
-      <sz val="7.5"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -205,32 +206,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -429,12 +428,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Drill par compte'!$K$35:$K$47</f>
+              <f>'Drill par compte'!$J$35:$J$47</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Drill par compte'!$L$35:$L$47</f>
+              <f>'Drill par compte'!$K$35:$K$47</f>
             </numRef>
           </val>
         </ser>
@@ -455,12 +454,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Drill par compte'!$K$35:$K$47</f>
+              <f>'Drill par compte'!$J$35:$J$47</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Drill par compte'!$M$35:$M$47</f>
+              <f>'Drill par compte'!$L$35:$L$47</f>
             </numRef>
           </val>
         </ser>
@@ -820,21 +819,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
     <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
     <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="8" customHeight="1">
@@ -847,7 +852,6 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="1" t="n"/>
@@ -863,13 +867,12 @@
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n"/>
       <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>drill sur la cellule cliquée · 2026 contre 2025 · comptes lus dans AW_002_000004_000001, CA reconstruit dans le socle CRM</t>
+          <t>drill sur la cellule cliquée · 2026 contre 2025 · le tableau lit la restitution de Q_D2_SOCLE par RECHERCHEV sur le compte</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -879,7 +882,6 @@
       <c r="G3" s="1" t="n"/>
       <c r="H3" s="1" t="n"/>
       <c r="I3" s="1" t="n"/>
-      <c r="J3" s="1" t="n"/>
     </row>
     <row r="4" ht="10" customHeight="1">
       <c r="A4" s="4" t="n"/>
@@ -891,12 +893,11 @@
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="5">
-        <f>"Sur "&amp;TEXT(G34,"#,##0 €")&amp;" de chiffre d'affaires, "&amp;TEXT(-SUM(G35:G47),"#,##0 €")&amp;" partent en charges. Il reste "&amp;TEXT(SUM(G34:G47),"#,##0 €")&amp;" d'EBITDA, soit "&amp;TEXT(SUM(G34:G47)/G34,"0.0%")&amp;" du chiffre d'affaires."</f>
+        <f>"Sur "&amp;TEXT(F34,"#,##0 €")&amp;" de chiffre d'affaires, "&amp;TEXT(-SUM(F35:F47),"#,##0 €")&amp;" partent en charges. Il reste "&amp;TEXT(SUM(F34:F47),"#,##0 €")&amp;" d'EBITDA, soit "&amp;TEXT(SUM(F34:F47)/F34,"0.0%")&amp;" du chiffre d'affaires."</f>
         <v/>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -906,13 +907,12 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>les charges ci-dessous sont signées en négatif : leur somme avec le CA donne l'EBITDA</t>
+          <t>les charges sont signées en négatif : leur somme avec le CA donne l'EBITDA</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -922,7 +922,36 @@
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>Compte</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>Poste court</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>Montant 2025</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>Montant 2026</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="8" customHeight="1">
       <c r="A7" s="4" t="n"/>
@@ -934,7 +963,32 @@
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Produits</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires (socle CRM)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>21758770</v>
+      </c>
+      <c r="S7" t="n">
+        <v>23098985</v>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="4" t="n"/>
@@ -946,7 +1000,32 @@
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Coût variable</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Personnel extérieur (vacataires)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Vacataires</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>-1509499</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1581554</v>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="4" t="n"/>
@@ -958,7 +1037,32 @@
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Coût variable</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Achats d'études</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Achats d'études</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>-646928</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-677808</v>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="4" t="n"/>
@@ -970,7 +1074,32 @@
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>6063</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Coût variable</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fournitures</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Fournitures</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>-431286</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-451874</v>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="4" t="n"/>
@@ -982,7 +1111,32 @@
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6231</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Coût variable</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Publicité et acquisition</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>-394702</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-434174</v>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="4" t="n"/>
@@ -994,7 +1148,32 @@
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n"/>
       <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6411</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Coûts directs</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Salaires des permanents</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Salaires</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>-3665791.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-3841069.840000001</v>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="4" t="n"/>
@@ -1006,7 +1185,32 @@
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>6413</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Coûts directs</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Primes</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Primes</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>-1940873.02</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-2033330.6</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="4" t="n"/>
@@ -1018,7 +1222,32 @@
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Coûts directs</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Charges sociales</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Charges sociales</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-3019137.459999999</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-3162957.9</v>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="4" t="n"/>
@@ -1030,7 +1259,32 @@
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Coûts directs</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Loyers</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Loyers</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>-2264167.84</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-2372423.51</v>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="4" t="n"/>
@@ -1042,7 +1296,32 @@
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Coûts directs</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Entretien</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Entretien</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>-323450.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-338915.38</v>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="4" t="n"/>
@@ -1054,7 +1333,32 @@
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Coûts directs</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Assurances</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Assurances</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>-215654.58</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-225926.43</v>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="4" t="n"/>
@@ -1066,7 +1370,32 @@
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Coûts directs</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Déplacements</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Déplacements</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>-323478.14</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-338890.3800000001</v>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="4" t="n"/>
@@ -1078,7 +1407,32 @@
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>63511</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Coûts directs</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>-215634.87</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-225943.95</v>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="4" t="n"/>
@@ -1090,7 +1444,32 @@
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>SIEGE</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Siège</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Siège redescendu (allocation, pas une écriture)</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Siège</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>-3340399.000000001</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-3568327</v>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="4" t="n"/>
@@ -1102,7 +1481,6 @@
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="4" t="n"/>
@@ -1114,7 +1492,6 @@
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="4" t="n"/>
       <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="4" t="n"/>
@@ -1126,7 +1503,6 @@
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="4" t="n"/>
@@ -1138,7 +1514,6 @@
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="4" t="n"/>
@@ -1150,7 +1525,6 @@
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="n"/>
       <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="4" t="n"/>
@@ -1162,7 +1536,6 @@
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="4" t="n"/>
       <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="4" t="n"/>
@@ -1174,7 +1547,6 @@
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="4" t="n"/>
       <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="4" t="n"/>
@@ -1186,7 +1558,6 @@
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="4" t="n"/>
@@ -1198,7 +1569,6 @@
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="4" t="n"/>
@@ -1210,7 +1580,6 @@
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="4" t="n"/>
       <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="4" t="n"/>
@@ -1222,11 +1591,10 @@
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="4" t="n"/>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>LE COMPTE D'EXPLOITATION, POSTE PAR POSTE</t>
         </is>
@@ -1236,63 +1604,57 @@
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ce que la requête renvoie · les deux dernières colonnes sont calculées  </t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="n"/>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colonnes C à F lues dans la restitution par RECHERCHEV · G et H calculées ici  </t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="4" t="n"/>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Rang</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Compte</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Famille</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Montant 2025</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Montant 2026</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Variation</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>Part des charges</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -1300,671 +1662,623 @@
     </row>
     <row r="34" ht="15.5" customHeight="1">
       <c r="A34" s="4" t="n"/>
-      <c r="B34" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Produits</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr"/>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>Chiffre d'affaires (socle CRM)</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="n">
-        <v>21758770</v>
-      </c>
-      <c r="G34" s="15" t="n">
-        <v>23098985</v>
-      </c>
-      <c r="H34" s="16">
-        <f>IF(F34=0,"",G34-F34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="17">
-        <f>IF(OR(B34="",B34=1),"",-G34/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Chiffre d'affaires</t>
-        </is>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="C34" s="13">
+        <f>IFERROR(VLOOKUP($B34,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="14">
+        <f>IFERROR(VLOOKUP($B34,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="15">
+        <f>IFERROR(VLOOKUP($B34,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F34" s="15">
+        <f>IFERROR(VLOOKUP($B34,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="16">
+        <f>F34-E34</f>
+        <v/>
+      </c>
+      <c r="H34" s="17">
+        <f>IF($B34="CA","",-F34/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34">
+        <f>IFERROR(VLOOKUP($B34,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
       <c r="A35" s="4" t="n"/>
-      <c r="B35" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Coût variable</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>621</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Personnel extérieur (vacataires)</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="n">
-        <v>-1509499</v>
-      </c>
-      <c r="G35" s="15" t="n">
-        <v>-1581554</v>
-      </c>
-      <c r="H35" s="16">
-        <f>IF(F35=0,"",G35-F35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="17">
-        <f>IF(OR(B35="",B35=1),"",-G35/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J35" s="4" t="n"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Vacataires</t>
-        </is>
+      <c r="C35" s="13">
+        <f>IFERROR(VLOOKUP($B35,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="14">
+        <f>IFERROR(VLOOKUP($B35,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="15">
+        <f>IFERROR(VLOOKUP($B35,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F35" s="15">
+        <f>IFERROR(VLOOKUP($B35,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G35" s="16">
+        <f>F35-E35</f>
+        <v/>
+      </c>
+      <c r="H35" s="17">
+        <f>IF($B35="CA","",-F35/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35">
+        <f>IFERROR(VLOOKUP($B35,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K35">
+        <f>-E35</f>
+        <v/>
       </c>
       <c r="L35">
         <f>-F35</f>
         <v/>
       </c>
-      <c r="M35">
-        <f>-G35</f>
-        <v/>
-      </c>
     </row>
     <row r="36" ht="15.5" customHeight="1">
       <c r="A36" s="4" t="n"/>
-      <c r="B36" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>Coût variable</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>604</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>Achats d'études</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="n">
-        <v>-646928</v>
-      </c>
-      <c r="G36" s="15" t="n">
-        <v>-677808</v>
-      </c>
-      <c r="H36" s="16">
-        <f>IF(F36=0,"",G36-F36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="17">
-        <f>IF(OR(B36="",B36=1),"",-G36/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Achats d'études</t>
-        </is>
+      <c r="C36" s="13">
+        <f>IFERROR(VLOOKUP($B36,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="14">
+        <f>IFERROR(VLOOKUP($B36,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="15">
+        <f>IFERROR(VLOOKUP($B36,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F36" s="15">
+        <f>IFERROR(VLOOKUP($B36,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G36" s="16">
+        <f>F36-E36</f>
+        <v/>
+      </c>
+      <c r="H36" s="17">
+        <f>IF($B36="CA","",-F36/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36">
+        <f>IFERROR(VLOOKUP($B36,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K36">
+        <f>-E36</f>
+        <v/>
       </c>
       <c r="L36">
         <f>-F36</f>
         <v/>
       </c>
-      <c r="M36">
-        <f>-G36</f>
-        <v/>
-      </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
       <c r="A37" s="4" t="n"/>
-      <c r="B37" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>Coût variable</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>6063</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Fournitures</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="n">
-        <v>-431286</v>
-      </c>
-      <c r="G37" s="15" t="n">
-        <v>-451874</v>
-      </c>
-      <c r="H37" s="16">
-        <f>IF(F37=0,"",G37-F37)</f>
-        <v/>
-      </c>
-      <c r="I37" s="17">
-        <f>IF(OR(B37="",B37=1),"",-G37/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Fournitures</t>
-        </is>
+      <c r="C37" s="13">
+        <f>IFERROR(VLOOKUP($B37,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="14">
+        <f>IFERROR(VLOOKUP($B37,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="15">
+        <f>IFERROR(VLOOKUP($B37,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F37" s="15">
+        <f>IFERROR(VLOOKUP($B37,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="16">
+        <f>F37-E37</f>
+        <v/>
+      </c>
+      <c r="H37" s="17">
+        <f>IF($B37="CA","",-F37/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37">
+        <f>IFERROR(VLOOKUP($B37,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K37">
+        <f>-E37</f>
+        <v/>
       </c>
       <c r="L37">
         <f>-F37</f>
         <v/>
       </c>
-      <c r="M37">
-        <f>-G37</f>
-        <v/>
-      </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
       <c r="A38" s="4" t="n"/>
-      <c r="B38" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>Coût variable</t>
-        </is>
-      </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>6231</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>Publicité et acquisition</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="n">
-        <v>-394702</v>
-      </c>
-      <c r="G38" s="15" t="n">
-        <v>-434174</v>
-      </c>
-      <c r="H38" s="16">
-        <f>IF(F38=0,"",G38-F38)</f>
-        <v/>
-      </c>
-      <c r="I38" s="17">
-        <f>IF(OR(B38="",B38=1),"",-G38/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Acquisition</t>
-        </is>
+      <c r="C38" s="13">
+        <f>IFERROR(VLOOKUP($B38,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="14">
+        <f>IFERROR(VLOOKUP($B38,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="15">
+        <f>IFERROR(VLOOKUP($B38,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F38" s="15">
+        <f>IFERROR(VLOOKUP($B38,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G38" s="16">
+        <f>F38-E38</f>
+        <v/>
+      </c>
+      <c r="H38" s="17">
+        <f>IF($B38="CA","",-F38/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38">
+        <f>IFERROR(VLOOKUP($B38,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K38">
+        <f>-E38</f>
+        <v/>
       </c>
       <c r="L38">
         <f>-F38</f>
         <v/>
       </c>
-      <c r="M38">
-        <f>-G38</f>
-        <v/>
-      </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
       <c r="A39" s="4" t="n"/>
-      <c r="B39" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>Coûts directs</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>6411</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Salaires des permanents</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>-3665791.33</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <v>-3841069.840000001</v>
-      </c>
-      <c r="H39" s="16">
-        <f>IF(F39=0,"",G39-F39)</f>
-        <v/>
-      </c>
-      <c r="I39" s="17">
-        <f>IF(OR(B39="",B39=1),"",-G39/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J39" s="4" t="n"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Salaires</t>
-        </is>
+      <c r="C39" s="13">
+        <f>IFERROR(VLOOKUP($B39,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="14">
+        <f>IFERROR(VLOOKUP($B39,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="15">
+        <f>IFERROR(VLOOKUP($B39,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F39" s="15">
+        <f>IFERROR(VLOOKUP($B39,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G39" s="16">
+        <f>F39-E39</f>
+        <v/>
+      </c>
+      <c r="H39" s="17">
+        <f>IF($B39="CA","",-F39/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39">
+        <f>IFERROR(VLOOKUP($B39,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K39">
+        <f>-E39</f>
+        <v/>
       </c>
       <c r="L39">
         <f>-F39</f>
         <v/>
       </c>
-      <c r="M39">
-        <f>-G39</f>
-        <v/>
-      </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
       <c r="A40" s="4" t="n"/>
-      <c r="B40" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>Coûts directs</t>
-        </is>
-      </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>6413</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>Primes</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="n">
-        <v>-1940873.02</v>
-      </c>
-      <c r="G40" s="15" t="n">
-        <v>-2033330.6</v>
-      </c>
-      <c r="H40" s="16">
-        <f>IF(F40=0,"",G40-F40)</f>
-        <v/>
-      </c>
-      <c r="I40" s="17">
-        <f>IF(OR(B40="",B40=1),"",-G40/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Primes</t>
-        </is>
+      <c r="C40" s="13">
+        <f>IFERROR(VLOOKUP($B40,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="14">
+        <f>IFERROR(VLOOKUP($B40,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="15">
+        <f>IFERROR(VLOOKUP($B40,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F40" s="15">
+        <f>IFERROR(VLOOKUP($B40,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G40" s="16">
+        <f>F40-E40</f>
+        <v/>
+      </c>
+      <c r="H40" s="17">
+        <f>IF($B40="CA","",-F40/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40">
+        <f>IFERROR(VLOOKUP($B40,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K40">
+        <f>-E40</f>
+        <v/>
       </c>
       <c r="L40">
         <f>-F40</f>
         <v/>
       </c>
-      <c r="M40">
-        <f>-G40</f>
-        <v/>
-      </c>
     </row>
     <row r="41" ht="15.5" customHeight="1">
       <c r="A41" s="4" t="n"/>
-      <c r="B41" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>Coûts directs</t>
-        </is>
-      </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>645</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>Charges sociales</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>-3019137.459999999</v>
-      </c>
-      <c r="G41" s="15" t="n">
-        <v>-3162957.9</v>
-      </c>
-      <c r="H41" s="16">
-        <f>IF(F41=0,"",G41-F41)</f>
-        <v/>
-      </c>
-      <c r="I41" s="17">
-        <f>IF(OR(B41="",B41=1),"",-G41/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Charges sociales</t>
-        </is>
+      <c r="C41" s="13">
+        <f>IFERROR(VLOOKUP($B41,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="14">
+        <f>IFERROR(VLOOKUP($B41,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="15">
+        <f>IFERROR(VLOOKUP($B41,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F41" s="15">
+        <f>IFERROR(VLOOKUP($B41,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G41" s="16">
+        <f>F41-E41</f>
+        <v/>
+      </c>
+      <c r="H41" s="17">
+        <f>IF($B41="CA","",-F41/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41">
+        <f>IFERROR(VLOOKUP($B41,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K41">
+        <f>-E41</f>
+        <v/>
       </c>
       <c r="L41">
         <f>-F41</f>
         <v/>
       </c>
-      <c r="M41">
-        <f>-G41</f>
-        <v/>
-      </c>
     </row>
     <row r="42" ht="15.5" customHeight="1">
       <c r="A42" s="4" t="n"/>
-      <c r="B42" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>Coûts directs</t>
-        </is>
-      </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>Loyers</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="n">
-        <v>-2264167.84</v>
-      </c>
-      <c r="G42" s="15" t="n">
-        <v>-2372423.51</v>
-      </c>
-      <c r="H42" s="16">
-        <f>IF(F42=0,"",G42-F42)</f>
-        <v/>
-      </c>
-      <c r="I42" s="17">
-        <f>IF(OR(B42="",B42=1),"",-G42/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Loyers</t>
-        </is>
+      <c r="C42" s="13">
+        <f>IFERROR(VLOOKUP($B42,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="14">
+        <f>IFERROR(VLOOKUP($B42,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="15">
+        <f>IFERROR(VLOOKUP($B42,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F42" s="15">
+        <f>IFERROR(VLOOKUP($B42,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G42" s="16">
+        <f>F42-E42</f>
+        <v/>
+      </c>
+      <c r="H42" s="17">
+        <f>IF($B42="CA","",-F42/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42">
+        <f>IFERROR(VLOOKUP($B42,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K42">
+        <f>-E42</f>
+        <v/>
       </c>
       <c r="L42">
         <f>-F42</f>
         <v/>
       </c>
-      <c r="M42">
-        <f>-G42</f>
-        <v/>
-      </c>
     </row>
     <row r="43" ht="15.5" customHeight="1">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>Coûts directs</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>615</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>Entretien</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="n">
-        <v>-323450.8</v>
-      </c>
-      <c r="G43" s="15" t="n">
-        <v>-338915.38</v>
-      </c>
-      <c r="H43" s="16">
-        <f>IF(F43=0,"",G43-F43)</f>
-        <v/>
-      </c>
-      <c r="I43" s="17">
-        <f>IF(OR(B43="",B43=1),"",-G43/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Entretien</t>
-        </is>
+      <c r="C43" s="13">
+        <f>IFERROR(VLOOKUP($B43,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="14">
+        <f>IFERROR(VLOOKUP($B43,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="15">
+        <f>IFERROR(VLOOKUP($B43,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F43" s="15">
+        <f>IFERROR(VLOOKUP($B43,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="16">
+        <f>F43-E43</f>
+        <v/>
+      </c>
+      <c r="H43" s="17">
+        <f>IF($B43="CA","",-F43/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43">
+        <f>IFERROR(VLOOKUP($B43,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K43">
+        <f>-E43</f>
+        <v/>
       </c>
       <c r="L43">
         <f>-F43</f>
         <v/>
       </c>
-      <c r="M43">
-        <f>-G43</f>
-        <v/>
-      </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>Coûts directs</t>
-        </is>
-      </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>616</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>Assurances</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="n">
-        <v>-215654.58</v>
-      </c>
-      <c r="G44" s="15" t="n">
-        <v>-225926.43</v>
-      </c>
-      <c r="H44" s="16">
-        <f>IF(F44=0,"",G44-F44)</f>
-        <v/>
-      </c>
-      <c r="I44" s="17">
-        <f>IF(OR(B44="",B44=1),"",-G44/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Assurances</t>
-        </is>
+      <c r="C44" s="13">
+        <f>IFERROR(VLOOKUP($B44,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="14">
+        <f>IFERROR(VLOOKUP($B44,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="15">
+        <f>IFERROR(VLOOKUP($B44,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F44" s="15">
+        <f>IFERROR(VLOOKUP($B44,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="16">
+        <f>F44-E44</f>
+        <v/>
+      </c>
+      <c r="H44" s="17">
+        <f>IF($B44="CA","",-F44/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44">
+        <f>IFERROR(VLOOKUP($B44,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K44">
+        <f>-E44</f>
+        <v/>
       </c>
       <c r="L44">
         <f>-F44</f>
         <v/>
       </c>
-      <c r="M44">
-        <f>-G44</f>
-        <v/>
-      </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
       <c r="A45" s="4" t="n"/>
-      <c r="B45" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>Coûts directs</t>
-        </is>
-      </c>
-      <c r="D45" s="13" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>625</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Déplacements</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>-323478.14</v>
-      </c>
-      <c r="G45" s="15" t="n">
-        <v>-338890.3800000001</v>
-      </c>
-      <c r="H45" s="16">
-        <f>IF(F45=0,"",G45-F45)</f>
-        <v/>
-      </c>
-      <c r="I45" s="17">
-        <f>IF(OR(B45="",B45=1),"",-G45/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Déplacements</t>
-        </is>
+      <c r="C45" s="13">
+        <f>IFERROR(VLOOKUP($B45,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="14">
+        <f>IFERROR(VLOOKUP($B45,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="15">
+        <f>IFERROR(VLOOKUP($B45,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F45" s="15">
+        <f>IFERROR(VLOOKUP($B45,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="16">
+        <f>F45-E45</f>
+        <v/>
+      </c>
+      <c r="H45" s="17">
+        <f>IF($B45="CA","",-F45/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45">
+        <f>IFERROR(VLOOKUP($B45,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K45">
+        <f>-E45</f>
+        <v/>
       </c>
       <c r="L45">
         <f>-F45</f>
         <v/>
       </c>
-      <c r="M45">
-        <f>-G45</f>
-        <v/>
-      </c>
     </row>
     <row r="46" ht="15.5" customHeight="1">
       <c r="A46" s="4" t="n"/>
-      <c r="B46" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>Coûts directs</t>
-        </is>
-      </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>63511</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>Taxes</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>-215634.87</v>
-      </c>
-      <c r="G46" s="15" t="n">
-        <v>-225943.95</v>
-      </c>
-      <c r="H46" s="16">
-        <f>IF(F46=0,"",G46-F46)</f>
-        <v/>
-      </c>
-      <c r="I46" s="17">
-        <f>IF(OR(B46="",B46=1),"",-G46/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Taxes</t>
-        </is>
+      <c r="C46" s="13">
+        <f>IFERROR(VLOOKUP($B46,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="14">
+        <f>IFERROR(VLOOKUP($B46,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="15">
+        <f>IFERROR(VLOOKUP($B46,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F46" s="15">
+        <f>IFERROR(VLOOKUP($B46,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G46" s="16">
+        <f>F46-E46</f>
+        <v/>
+      </c>
+      <c r="H46" s="17">
+        <f>IF($B46="CA","",-F46/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46">
+        <f>IFERROR(VLOOKUP($B46,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K46">
+        <f>-E46</f>
+        <v/>
       </c>
       <c r="L46">
         <f>-F46</f>
         <v/>
       </c>
-      <c r="M46">
-        <f>-G46</f>
-        <v/>
-      </c>
     </row>
     <row r="47" ht="15.5" customHeight="1">
       <c r="A47" s="4" t="n"/>
-      <c r="B47" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>Siège</t>
-        </is>
-      </c>
-      <c r="D47" s="13" t="inlineStr"/>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Siège redescendu (allocation, pas une écriture)</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="n">
-        <v>-3340399.000000001</v>
-      </c>
-      <c r="G47" s="15" t="n">
-        <v>-3568327</v>
-      </c>
-      <c r="H47" s="16">
-        <f>IF(F47=0,"",G47-F47)</f>
-        <v/>
-      </c>
-      <c r="I47" s="17">
-        <f>IF(OR(B47="",B47=1),"",-G47/SUM(G35:G47))</f>
-        <v/>
-      </c>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Siège</t>
-        </is>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>SIEGE</t>
+        </is>
+      </c>
+      <c r="C47" s="13">
+        <f>IFERROR(VLOOKUP($B47,$N$7:$S$26,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="14">
+        <f>IFERROR(VLOOKUP($B47,$N$7:$S$26,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="15">
+        <f>IFERROR(VLOOKUP($B47,$N$7:$S$26,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F47" s="15">
+        <f>IFERROR(VLOOKUP($B47,$N$7:$S$26,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="16">
+        <f>F47-E47</f>
+        <v/>
+      </c>
+      <c r="H47" s="17">
+        <f>IF($B47="CA","",-F47/SUM(F35:F47))</f>
+        <v/>
+      </c>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47">
+        <f>IFERROR(VLOOKUP($B47,$N$7:$S$26,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K47">
+        <f>-E47</f>
+        <v/>
       </c>
       <c r="L47">
         <f>-F47</f>
-        <v/>
-      </c>
-      <c r="M47">
-        <f>-G47</f>
         <v/>
       </c>
     </row>
@@ -1978,7 +2292,6 @@
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="n"/>
-      <c r="J48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n"/>
@@ -1988,23 +2301,22 @@
         </is>
       </c>
       <c r="C49" s="19" t="n"/>
-      <c r="D49" s="19" t="n"/>
-      <c r="E49" s="18" t="inlineStr">
+      <c r="D49" s="18" t="inlineStr">
         <is>
           <t>la somme des quatorze lignes doit valoir l'EBITDA</t>
         </is>
+      </c>
+      <c r="E49" s="20">
+        <f>SUM(E34:E47)</f>
+        <v/>
       </c>
       <c r="F49" s="20">
         <f>SUM(F34:F47)</f>
         <v/>
       </c>
-      <c r="G49" s="20">
-        <f>SUM(G34:G47)</f>
-        <v/>
-      </c>
+      <c r="G49" s="19" t="n"/>
       <c r="H49" s="19" t="n"/>
-      <c r="I49" s="19" t="n"/>
-      <c r="J49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n"/>
@@ -2016,11 +2328,10 @@
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="n"/>
-      <c r="J50" s="4" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="4" t="n"/>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>RAPPROCHEMENT DU CHIFFRE D'AFFAIRES  ·  gestion contre socle CRM</t>
         </is>
@@ -2032,7 +2343,6 @@
       <c r="G51" s="4" t="n"/>
       <c r="H51" s="4" t="n"/>
       <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n"/>
@@ -2043,16 +2353,15 @@
       </c>
       <c r="C52" s="22" t="n"/>
       <c r="D52" s="22" t="n"/>
-      <c r="E52" s="22" t="n"/>
+      <c r="E52" s="23" t="n">
+        <v>21775820</v>
+      </c>
       <c r="F52" s="23" t="n">
-        <v>21775820</v>
-      </c>
-      <c r="G52" s="23" t="n">
         <v>23098985</v>
       </c>
+      <c r="G52" s="22" t="n"/>
       <c r="H52" s="22" t="n"/>
-      <c r="I52" s="22" t="n"/>
-      <c r="J52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n"/>
@@ -2063,16 +2372,15 @@
       </c>
       <c r="C53" s="22" t="n"/>
       <c r="D53" s="22" t="n"/>
-      <c r="E53" s="22" t="n"/>
+      <c r="E53" s="23" t="n">
+        <v>21758770</v>
+      </c>
       <c r="F53" s="23" t="n">
-        <v>21758770</v>
-      </c>
-      <c r="G53" s="23" t="n">
         <v>23098985</v>
       </c>
+      <c r="G53" s="22" t="n"/>
       <c r="H53" s="22" t="n"/>
-      <c r="I53" s="22" t="n"/>
-      <c r="J53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n"/>
@@ -2083,24 +2391,23 @@
       </c>
       <c r="C54" s="25" t="n"/>
       <c r="D54" s="25" t="n"/>
-      <c r="E54" s="25" t="n"/>
+      <c r="E54" s="26">
+        <f>E52-E53</f>
+        <v/>
+      </c>
       <c r="F54" s="26">
         <f>F52-F53</f>
         <v/>
       </c>
-      <c r="G54" s="26">
-        <f>G52-G53</f>
+      <c r="G54" s="27">
+        <f>E54/E53</f>
         <v/>
       </c>
       <c r="H54" s="27">
         <f>F54/F53</f>
         <v/>
       </c>
-      <c r="I54" s="27">
-        <f>G54/G53</f>
-        <v/>
-      </c>
-      <c r="J54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
@@ -2112,7 +2419,6 @@
       <c r="G55" s="4" t="n"/>
       <c r="H55" s="4" t="n"/>
       <c r="I55" s="4" t="n"/>
-      <c r="J55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n"/>
@@ -2128,7 +2434,6 @@
       <c r="G56" s="4" t="n"/>
       <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="n"/>
-      <c r="J56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n"/>
@@ -2144,7 +2449,6 @@
       <c r="G57" s="4" t="n"/>
       <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="n"/>
-      <c r="J57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n"/>
@@ -2160,7 +2464,6 @@
       <c r="G58" s="4" t="n"/>
       <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n"/>
@@ -2176,7 +2479,6 @@
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="n"/>
-      <c r="J59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n"/>
@@ -2188,7 +2490,6 @@
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="n"/>
-      <c r="J60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n"/>
@@ -2200,7 +2501,6 @@
       <c r="G61" s="4" t="n"/>
       <c r="H61" s="4" t="n"/>
       <c r="I61" s="4" t="n"/>
-      <c r="J61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n"/>
@@ -2212,7 +2512,6 @@
       <c r="G62" s="4" t="n"/>
       <c r="H62" s="4" t="n"/>
       <c r="I62" s="4" t="n"/>
-      <c r="J62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n"/>
@@ -2224,7 +2523,6 @@
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="4" t="n"/>
       <c r="I63" s="4" t="n"/>
-      <c r="J63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n"/>
@@ -2236,21 +2534,20 @@
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B34:I47">
+  <conditionalFormatting sqref="B34:H47">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$B34=1</formula>
+      <formula>$B34="CA"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$B34=14</formula>
+      <formula>$B34="SIEGE"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>$B34&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H47">
+  <conditionalFormatting sqref="G34:G47">
     <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -2258,11 +2555,11 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I34:I47">
+  <conditionalFormatting sqref="H34:H47">
     <cfRule type="dataBar" priority="6">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.3"/>
+        <cfvo type="max"/>
         <color rgb="FFB8CFEC"/>
       </dataBar>
     </cfRule>

--- a/eduservices/DRILL2_EXCEL.xlsx
+++ b/eduservices/DRILL2_EXCEL.xlsx
@@ -1558,6 +1558,21 @@
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="n"/>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>Controle</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>Montant 2025</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>Montant 2026</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="4" t="n"/>
@@ -1569,6 +1584,17 @@
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires en gestion (706 + 7062 + 708)</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>21775820</v>
+      </c>
+      <c r="P29" t="n">
+        <v>23098985</v>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="4" t="n"/>
@@ -2353,11 +2379,13 @@
       </c>
       <c r="C52" s="22" t="n"/>
       <c r="D52" s="22" t="n"/>
-      <c r="E52" s="23" t="n">
-        <v>21775820</v>
-      </c>
-      <c r="F52" s="23" t="n">
-        <v>23098985</v>
+      <c r="E52" s="23">
+        <f>$O$29</f>
+        <v/>
+      </c>
+      <c r="F52" s="23">
+        <f>$P$29</f>
+        <v/>
       </c>
       <c r="G52" s="22" t="n"/>
       <c r="H52" s="22" t="n"/>
@@ -2372,11 +2400,13 @@
       </c>
       <c r="C53" s="22" t="n"/>
       <c r="D53" s="22" t="n"/>
-      <c r="E53" s="23" t="n">
-        <v>21758770</v>
-      </c>
-      <c r="F53" s="23" t="n">
-        <v>23098985</v>
+      <c r="E53" s="23">
+        <f>E34</f>
+        <v/>
+      </c>
+      <c r="F53" s="23">
+        <f>F34</f>
+        <v/>
       </c>
       <c r="G53" s="22" t="n"/>
       <c r="H53" s="22" t="n"/>
@@ -2424,7 +2454,7 @@
       <c r="A56" s="4" t="n"/>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>L'écart est normal et n'est pas corrigé : cette table porte l'ESTIMÉ, pas un grand livre clôturé. Sept centièmes de pour cent entre un estimé et un modèle piloté par les inducteurs, c'est le fonctionnement des deux chaînes.</t>
+          <t>Ce rapprochement est un CONTRÔLE, pas une source. V_ALLOCATION ne lit jamais les comptes de produit : le chiffre d'affaires du modèle vient du socle CRM, quoi que disent le 706, le 7062 et le 708.</t>
         </is>
       </c>
       <c r="C56" s="4" t="n"/>
@@ -2439,7 +2469,7 @@
       <c r="A57" s="4" t="n"/>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>2026 tombe au centime parce que l'exercice est construit depuis le socle, donc aligné par construction. Les exercices passés portent un estimé établi séparément.</t>
+          <t>Le modèle prend le CRM pour deux raisons qui ne tiennent pas à l'exactitude. Le GRAIN — 180 lignes campus × programme × année × modalité contre 105 au grain campus × compte, sans quoi aucune marge par programme n'est calculable.</t>
         </is>
       </c>
       <c r="C57" s="4" t="n"/>
@@ -2454,7 +2484,7 @@
       <c r="A58" s="4" t="n"/>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Le modèle prend le CRM pour deux raisons qui ne tiennent pas à l'exactitude. Le GRAIN — 180 lignes campus × programme × année × modalité contre 105 au grain campus × compte, sans quoi aucune marge par programme n'est calculable.</t>
+          <t>Et le PILOTAGE — le CRM donne le CA comme un produit d'inducteurs, effectifs × droits de scolarité, donc il se simule. Un montant déjà posé est un constat.</t>
         </is>
       </c>
       <c r="C58" s="4" t="n"/>
@@ -2469,7 +2499,7 @@
       <c r="A59" s="4" t="n"/>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>Et le PILOTAGE — le CRM donne le CA comme un produit d'inducteurs, effectifs × droits de scolarité, donc il se simule. Un montant déjà posé est un constat.</t>
+          <t>2026 tombe au centime parce que l'exercice est construit depuis le socle. 2024 et 2025 portaient un estimé établi séparément, à ± 0,08 % près ; FIX_CA_COMPTA_2024_2025.sql les réaligne sur le CRM en un UPDATE de 70 lignes.</t>
         </is>
       </c>
       <c r="C59" s="4" t="n"/>

--- a/eduservices/DRILL2_EXCEL.xlsx
+++ b/eduservices/DRILL2_EXCEL.xlsx
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>21775820</v>
+        <v>21758770</v>
       </c>
       <c r="P29" t="n">
         <v>23098985</v>
@@ -2499,7 +2499,7 @@
       <c r="A59" s="4" t="n"/>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>2026 tombe au centime parce que l'exercice est construit depuis le socle. 2024 et 2025 portaient un estimé établi séparément, à ± 0,08 % près ; FIX_CA_COMPTA_2024_2025.sql les réaligne sur le CRM en un UPDATE de 70 lignes.</t>
+          <t>Les trois exercices tombent désormais au centime. 2024 et 2025 portaient un estimé établi séparément, à ± 0,08 % près ; FIX_CA_COMPTA_2024_2025.sql les a réalignés sur le CRM, 70 lignes recalculées et pas un centime d'EBITDA déplacé.</t>
         </is>
       </c>
       <c r="C59" s="4" t="n"/>

--- a/eduservices/DRILL2_EXCEL.xlsx
+++ b/eduservices/DRILL2_EXCEL.xlsx
@@ -428,12 +428,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Drill par compte'!$J$35:$J$47</f>
+              <f>'Drill par compte'!$J$37:$J$49</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Drill par compte'!$K$35:$K$47</f>
+              <f>'Drill par compte'!$K$37:$K$49</f>
             </numRef>
           </val>
         </ser>
@@ -454,12 +454,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Drill par compte'!$J$35:$J$47</f>
+              <f>'Drill par compte'!$J$37:$J$49</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Drill par compte'!$L$35:$L$47</f>
+              <f>'Drill par compte'!$L$37:$L$49</f>
             </numRef>
           </val>
         </ser>
@@ -819,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S64"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -840,6 +840,8 @@
     <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
     <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
     <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="8" customHeight="1">
@@ -872,7 +874,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>drill sur la cellule cliquée · 2026 contre 2025 · le tableau lit la restitution de Q_D2_SOCLE par RECHERCHEV sur le compte</t>
+          <t>drill sur la cellule cliquée · 2026 contre 2025 · quinze comptes lus dans AW_002_000004_000001, plus le siège redescendu</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -897,7 +899,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="5">
-        <f>"Sur "&amp;TEXT(F34,"#,##0 €")&amp;" de chiffre d'affaires, "&amp;TEXT(-SUM(F35:F47),"#,##0 €")&amp;" partent en charges. Il reste "&amp;TEXT(SUM(F34:F47),"#,##0 €")&amp;" d'EBITDA, soit "&amp;TEXT(SUM(F34:F47)/F34,"0.0%")&amp;" du chiffre d'affaires."</f>
+        <f>"Sur "&amp;TEXT(SUM(F34:F36),"#,##0 €")&amp;" de chiffre d'affaires, "&amp;TEXT(-SUM(F37:F49),"#,##0 €")&amp;" partent en charges. Il reste "&amp;TEXT(SUM(F34:F49),"#,##0 €")&amp;" d'EBITDA, soit "&amp;TEXT(SUM(F34:F49)/SUM(F34:F36),"0.0%")&amp;" du chiffre d'affaires."</f>
         <v/>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -912,7 +914,7 @@
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>les charges sont signées en négatif : leur somme avec le CA donne l'EBITDA</t>
+          <t>les charges sont signées en négatif : leur somme avec les produits donne l'EBITDA</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -965,7 +967,7 @@
       <c r="I7" s="4" t="n"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>706</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -975,19 +977,19 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Chiffre d'affaires (socle CRM)</t>
+          <t>Scolarité des étudiants en initial</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Chiffre d'affaires</t>
+          <t>Scolarité initial</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>21758770</v>
+        <v>3120000</v>
       </c>
       <c r="S7" t="n">
-        <v>23098985</v>
+        <v>3306675</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -1002,29 +1004,29 @@
       <c r="I8" s="4" t="n"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Coût variable</t>
+          <t>Produits</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Personnel extérieur (vacataires)</t>
+          <t>Scolarité des alternants</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Vacataires</t>
+          <t>Scolarité alternance</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>-1509499</v>
+        <v>18534460</v>
       </c>
       <c r="S8" t="n">
-        <v>-1581554</v>
+        <v>19681700</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -1039,29 +1041,29 @@
       <c r="I9" s="4" t="n"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>708</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Coût variable</t>
+          <t>Produits</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Achats d'études</t>
+          <t>Frais d'inscription</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Achats d'études</t>
+          <t>Frais d'inscription</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>-646928</v>
+        <v>104310</v>
       </c>
       <c r="S9" t="n">
-        <v>-677808</v>
+        <v>110610</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -1076,7 +1078,7 @@
       <c r="I10" s="4" t="n"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>621</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1086,19 +1088,19 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fournitures</t>
+          <t>Personnel extérieur (vacataires)</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Fournitures</t>
+          <t>Vacataires</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>-431286</v>
+        <v>-1509499</v>
       </c>
       <c r="S10" t="n">
-        <v>-451874</v>
+        <v>-1581554</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -1113,7 +1115,7 @@
       <c r="I11" s="4" t="n"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>604</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1123,19 +1125,19 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Publicité et acquisition</t>
+          <t>Achats d'études</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Achats d'études</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-394702</v>
+        <v>-646928</v>
       </c>
       <c r="S11" t="n">
-        <v>-434174</v>
+        <v>-677808</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -1150,29 +1152,29 @@
       <c r="I12" s="4" t="n"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Coûts directs</t>
+          <t>Coût variable</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Salaires des permanents</t>
+          <t>Fournitures</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Salaires</t>
+          <t>Fournitures</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-3665791.33</v>
+        <v>-431286</v>
       </c>
       <c r="S12" t="n">
-        <v>-3841069.840000001</v>
+        <v>-451874</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -1187,29 +1189,29 @@
       <c r="I13" s="4" t="n"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Coûts directs</t>
+          <t>Coût variable</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Primes</t>
+          <t>Publicité et acquisition</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Primes</t>
+          <t>Acquisition</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-1940873.02</v>
+        <v>-394702</v>
       </c>
       <c r="S13" t="n">
-        <v>-2033330.6</v>
+        <v>-434174</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -1224,7 +1226,7 @@
       <c r="I14" s="4" t="n"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1234,19 +1236,19 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Charges sociales</t>
+          <t>Salaires des permanents</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Charges sociales</t>
+          <t>Salaires</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-3019137.459999999</v>
+        <v>-3665791.33</v>
       </c>
       <c r="S14" t="n">
-        <v>-3162957.9</v>
+        <v>-3841069.840000001</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -1261,7 +1263,7 @@
       <c r="I15" s="4" t="n"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1271,19 +1273,19 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Loyers</t>
+          <t>Primes</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Loyers</t>
+          <t>Primes</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>-2264167.84</v>
+        <v>-1940873.02</v>
       </c>
       <c r="S15" t="n">
-        <v>-2372423.51</v>
+        <v>-2033330.6</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -1298,7 +1300,7 @@
       <c r="I16" s="4" t="n"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>645</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1308,19 +1310,19 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Entretien</t>
+          <t>Charges sociales</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Entretien</t>
+          <t>Charges sociales</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>-323450.8</v>
+        <v>-3019137.459999999</v>
       </c>
       <c r="S16" t="n">
-        <v>-338915.38</v>
+        <v>-3162957.9</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1335,7 +1337,7 @@
       <c r="I17" s="4" t="n"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>613</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1345,19 +1347,19 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assurances</t>
+          <t>Loyers</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Assurances</t>
+          <t>Loyers</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>-215654.58</v>
+        <v>-2264167.84</v>
       </c>
       <c r="S17" t="n">
-        <v>-225926.43</v>
+        <v>-2372423.51</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1372,7 +1374,7 @@
       <c r="I18" s="4" t="n"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>615</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1382,19 +1384,19 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Déplacements</t>
+          <t>Entretien</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Déplacements</t>
+          <t>Entretien</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>-323478.14</v>
+        <v>-323450.8</v>
       </c>
       <c r="S18" t="n">
-        <v>-338890.3800000001</v>
+        <v>-338915.38</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1409,7 +1411,7 @@
       <c r="I19" s="4" t="n"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>63511</t>
+          <t>616</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1419,19 +1421,19 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Assurances</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Assurances</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>-215634.87</v>
+        <v>-215654.58</v>
       </c>
       <c r="S19" t="n">
-        <v>-225943.95</v>
+        <v>-225926.43</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1446,29 +1448,29 @@
       <c r="I20" s="4" t="n"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>SIEGE</t>
+          <t>625</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Siège</t>
+          <t>Coûts directs</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Siège redescendu (allocation, pas une écriture)</t>
+          <t>Déplacements</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Siège</t>
+          <t>Déplacements</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>-3340399.000000001</v>
+        <v>-323478.14</v>
       </c>
       <c r="S20" t="n">
-        <v>-3568327</v>
+        <v>-338890.3800000001</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -1481,6 +1483,32 @@
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>63511</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Coûts directs</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>-215634.87</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-225943.95</v>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="4" t="n"/>
@@ -1492,6 +1520,32 @@
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="4" t="n"/>
       <c r="I22" s="4" t="n"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>SIEGE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Siège</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Siège redescendu (allocation, pas une écriture)</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Siège</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>-3340399.000000001</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-3568327</v>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="4" t="n"/>
@@ -1558,21 +1612,6 @@
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="n"/>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>Controle</t>
-        </is>
-      </c>
-      <c r="O28" s="7" t="inlineStr">
-        <is>
-          <t>Montant 2025</t>
-        </is>
-      </c>
-      <c r="P28" s="7" t="inlineStr">
-        <is>
-          <t>Montant 2026</t>
-        </is>
-      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="4" t="n"/>
@@ -1584,17 +1623,6 @@
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Chiffre d'affaires en gestion (706 + 7062 + 708)</t>
-        </is>
-      </c>
-      <c r="O29" t="n">
-        <v>21758770</v>
-      </c>
-      <c r="P29" t="n">
-        <v>23098985</v>
-      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="4" t="n"/>
@@ -1606,6 +1634,46 @@
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="4" t="n"/>
       <c r="I30" s="4" t="n"/>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>Compte</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>Poste court</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>Unite comptee</t>
+        </is>
+      </c>
+      <c r="R30" s="7" t="inlineStr">
+        <is>
+          <t>Volume 2025</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>Volume 2026</t>
+        </is>
+      </c>
+      <c r="T30" s="7" t="inlineStr">
+        <is>
+          <t>Montant 2025</t>
+        </is>
+      </c>
+      <c r="U30" s="7" t="inlineStr">
+        <is>
+          <t>Montant 2026</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="4" t="n"/>
@@ -1617,6 +1685,38 @@
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Scolarité des étudiants en initial</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Scolarité initial</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Effectifs</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>400</v>
+      </c>
+      <c r="S31" t="n">
+        <v>424</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3120000</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3306675</v>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="4" t="n"/>
@@ -1636,6 +1736,38 @@
         </is>
       </c>
       <c r="I32" s="4" t="n"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>7062</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Scolarité des alternants</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Scolarité alternance</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Effectifs</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>2533</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2690</v>
+      </c>
+      <c r="T32" t="n">
+        <v>18534460</v>
+      </c>
+      <c r="U32" t="n">
+        <v>19681700</v>
+      </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="4" t="n"/>
@@ -1685,28 +1817,60 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Frais d'inscription</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Frais d'inscription</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Nouveaux inscrits</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>1159</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1229</v>
+      </c>
+      <c r="T33" t="n">
+        <v>104310</v>
+      </c>
+      <c r="U33" t="n">
+        <v>110610</v>
+      </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
       <c r="A34" s="4" t="n"/>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>706</t>
         </is>
       </c>
       <c r="C34" s="13">
-        <f>IFERROR(VLOOKUP($B34,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B34,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D34" s="14">
-        <f>IFERROR(VLOOKUP($B34,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B34,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E34" s="15">
-        <f>IFERROR(VLOOKUP($B34,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B34,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F34" s="15">
-        <f>IFERROR(VLOOKUP($B34,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B34,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G34" s="16">
@@ -1714,12 +1878,12 @@
         <v/>
       </c>
       <c r="H34" s="17">
-        <f>IF($B34="CA","",-F34/SUM(F35:F47))</f>
+        <f>IF($C34="Produits","",-F34/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I34" s="4" t="n"/>
       <c r="J34">
-        <f>IFERROR(VLOOKUP($B34,$N$7:$S$26,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B34,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -1727,23 +1891,23 @@
       <c r="A35" s="4" t="n"/>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="C35" s="13">
-        <f>IFERROR(VLOOKUP($B35,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B35,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D35" s="14">
-        <f>IFERROR(VLOOKUP($B35,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B35,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E35" s="15">
-        <f>IFERROR(VLOOKUP($B35,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B35,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F35" s="15">
-        <f>IFERROR(VLOOKUP($B35,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B35,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G35" s="16">
@@ -1751,20 +1915,12 @@
         <v/>
       </c>
       <c r="H35" s="17">
-        <f>IF($B35="CA","",-F35/SUM(F35:F47))</f>
+        <f>IF($C35="Produits","",-F35/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I35" s="4" t="n"/>
       <c r="J35">
-        <f>IFERROR(VLOOKUP($B35,$N$7:$S$26,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="K35">
-        <f>-E35</f>
-        <v/>
-      </c>
-      <c r="L35">
-        <f>-F35</f>
+        <f>IFERROR(VLOOKUP($B35,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -1772,23 +1928,23 @@
       <c r="A36" s="4" t="n"/>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>708</t>
         </is>
       </c>
       <c r="C36" s="13">
-        <f>IFERROR(VLOOKUP($B36,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B36,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D36" s="14">
-        <f>IFERROR(VLOOKUP($B36,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B36,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E36" s="15">
-        <f>IFERROR(VLOOKUP($B36,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B36,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F36" s="15">
-        <f>IFERROR(VLOOKUP($B36,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B36,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G36" s="16">
@@ -1796,20 +1952,12 @@
         <v/>
       </c>
       <c r="H36" s="17">
-        <f>IF($B36="CA","",-F36/SUM(F35:F47))</f>
+        <f>IF($C36="Produits","",-F36/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I36" s="4" t="n"/>
       <c r="J36">
-        <f>IFERROR(VLOOKUP($B36,$N$7:$S$26,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="K36">
-        <f>-E36</f>
-        <v/>
-      </c>
-      <c r="L36">
-        <f>-F36</f>
+        <f>IFERROR(VLOOKUP($B36,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
@@ -1817,23 +1965,23 @@
       <c r="A37" s="4" t="n"/>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>621</t>
         </is>
       </c>
       <c r="C37" s="13">
-        <f>IFERROR(VLOOKUP($B37,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B37,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D37" s="14">
-        <f>IFERROR(VLOOKUP($B37,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B37,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E37" s="15">
-        <f>IFERROR(VLOOKUP($B37,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B37,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F37" s="15">
-        <f>IFERROR(VLOOKUP($B37,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B37,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G37" s="16">
@@ -1841,12 +1989,12 @@
         <v/>
       </c>
       <c r="H37" s="17">
-        <f>IF($B37="CA","",-F37/SUM(F35:F47))</f>
+        <f>IF($C37="Produits","",-F37/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I37" s="4" t="n"/>
       <c r="J37">
-        <f>IFERROR(VLOOKUP($B37,$N$7:$S$26,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B37,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="K37">
@@ -1862,23 +2010,23 @@
       <c r="A38" s="4" t="n"/>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>604</t>
         </is>
       </c>
       <c r="C38" s="13">
-        <f>IFERROR(VLOOKUP($B38,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B38,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D38" s="14">
-        <f>IFERROR(VLOOKUP($B38,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B38,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E38" s="15">
-        <f>IFERROR(VLOOKUP($B38,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B38,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F38" s="15">
-        <f>IFERROR(VLOOKUP($B38,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B38,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G38" s="16">
@@ -1886,12 +2034,12 @@
         <v/>
       </c>
       <c r="H38" s="17">
-        <f>IF($B38="CA","",-F38/SUM(F35:F47))</f>
+        <f>IF($C38="Produits","",-F38/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I38" s="4" t="n"/>
       <c r="J38">
-        <f>IFERROR(VLOOKUP($B38,$N$7:$S$26,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B38,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="K38">
@@ -1907,23 +2055,23 @@
       <c r="A39" s="4" t="n"/>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="C39" s="13">
-        <f>IFERROR(VLOOKUP($B39,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B39,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D39" s="14">
-        <f>IFERROR(VLOOKUP($B39,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B39,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E39" s="15">
-        <f>IFERROR(VLOOKUP($B39,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B39,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F39" s="15">
-        <f>IFERROR(VLOOKUP($B39,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B39,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G39" s="16">
@@ -1931,12 +2079,12 @@
         <v/>
       </c>
       <c r="H39" s="17">
-        <f>IF($B39="CA","",-F39/SUM(F35:F47))</f>
+        <f>IF($C39="Produits","",-F39/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I39" s="4" t="n"/>
       <c r="J39">
-        <f>IFERROR(VLOOKUP($B39,$N$7:$S$26,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B39,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="K39">
@@ -1952,23 +2100,23 @@
       <c r="A40" s="4" t="n"/>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="C40" s="13">
-        <f>IFERROR(VLOOKUP($B40,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B40,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D40" s="14">
-        <f>IFERROR(VLOOKUP($B40,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B40,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E40" s="15">
-        <f>IFERROR(VLOOKUP($B40,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B40,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F40" s="15">
-        <f>IFERROR(VLOOKUP($B40,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B40,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G40" s="16">
@@ -1976,12 +2124,12 @@
         <v/>
       </c>
       <c r="H40" s="17">
-        <f>IF($B40="CA","",-F40/SUM(F35:F47))</f>
+        <f>IF($C40="Produits","",-F40/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I40" s="4" t="n"/>
       <c r="J40">
-        <f>IFERROR(VLOOKUP($B40,$N$7:$S$26,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B40,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="K40">
@@ -1997,23 +2145,23 @@
       <c r="A41" s="4" t="n"/>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="C41" s="13">
-        <f>IFERROR(VLOOKUP($B41,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B41,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D41" s="14">
-        <f>IFERROR(VLOOKUP($B41,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B41,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E41" s="15">
-        <f>IFERROR(VLOOKUP($B41,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B41,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F41" s="15">
-        <f>IFERROR(VLOOKUP($B41,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B41,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G41" s="16">
@@ -2021,12 +2169,12 @@
         <v/>
       </c>
       <c r="H41" s="17">
-        <f>IF($B41="CA","",-F41/SUM(F35:F47))</f>
+        <f>IF($C41="Produits","",-F41/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I41" s="4" t="n"/>
       <c r="J41">
-        <f>IFERROR(VLOOKUP($B41,$N$7:$S$26,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B41,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="K41">
@@ -2042,23 +2190,23 @@
       <c r="A42" s="4" t="n"/>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="C42" s="13">
-        <f>IFERROR(VLOOKUP($B42,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B42,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D42" s="14">
-        <f>IFERROR(VLOOKUP($B42,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B42,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E42" s="15">
-        <f>IFERROR(VLOOKUP($B42,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B42,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F42" s="15">
-        <f>IFERROR(VLOOKUP($B42,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B42,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G42" s="16">
@@ -2066,12 +2214,12 @@
         <v/>
       </c>
       <c r="H42" s="17">
-        <f>IF($B42="CA","",-F42/SUM(F35:F47))</f>
+        <f>IF($C42="Produits","",-F42/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I42" s="4" t="n"/>
       <c r="J42">
-        <f>IFERROR(VLOOKUP($B42,$N$7:$S$26,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B42,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="K42">
@@ -2087,23 +2235,23 @@
       <c r="A43" s="4" t="n"/>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>645</t>
         </is>
       </c>
       <c r="C43" s="13">
-        <f>IFERROR(VLOOKUP($B43,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B43,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D43" s="14">
-        <f>IFERROR(VLOOKUP($B43,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B43,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E43" s="15">
-        <f>IFERROR(VLOOKUP($B43,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B43,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F43" s="15">
-        <f>IFERROR(VLOOKUP($B43,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B43,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G43" s="16">
@@ -2111,12 +2259,12 @@
         <v/>
       </c>
       <c r="H43" s="17">
-        <f>IF($B43="CA","",-F43/SUM(F35:F47))</f>
+        <f>IF($C43="Produits","",-F43/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I43" s="4" t="n"/>
       <c r="J43">
-        <f>IFERROR(VLOOKUP($B43,$N$7:$S$26,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B43,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="K43">
@@ -2132,23 +2280,23 @@
       <c r="A44" s="4" t="n"/>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>613</t>
         </is>
       </c>
       <c r="C44" s="13">
-        <f>IFERROR(VLOOKUP($B44,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B44,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D44" s="14">
-        <f>IFERROR(VLOOKUP($B44,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B44,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E44" s="15">
-        <f>IFERROR(VLOOKUP($B44,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B44,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F44" s="15">
-        <f>IFERROR(VLOOKUP($B44,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B44,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G44" s="16">
@@ -2156,12 +2304,12 @@
         <v/>
       </c>
       <c r="H44" s="17">
-        <f>IF($B44="CA","",-F44/SUM(F35:F47))</f>
+        <f>IF($C44="Produits","",-F44/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I44" s="4" t="n"/>
       <c r="J44">
-        <f>IFERROR(VLOOKUP($B44,$N$7:$S$26,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B44,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="K44">
@@ -2177,23 +2325,23 @@
       <c r="A45" s="4" t="n"/>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>615</t>
         </is>
       </c>
       <c r="C45" s="13">
-        <f>IFERROR(VLOOKUP($B45,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B45,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D45" s="14">
-        <f>IFERROR(VLOOKUP($B45,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B45,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E45" s="15">
-        <f>IFERROR(VLOOKUP($B45,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B45,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F45" s="15">
-        <f>IFERROR(VLOOKUP($B45,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B45,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G45" s="16">
@@ -2201,12 +2349,12 @@
         <v/>
       </c>
       <c r="H45" s="17">
-        <f>IF($B45="CA","",-F45/SUM(F35:F47))</f>
+        <f>IF($C45="Produits","",-F45/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I45" s="4" t="n"/>
       <c r="J45">
-        <f>IFERROR(VLOOKUP($B45,$N$7:$S$26,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B45,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="K45">
@@ -2222,23 +2370,23 @@
       <c r="A46" s="4" t="n"/>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>63511</t>
+          <t>616</t>
         </is>
       </c>
       <c r="C46" s="13">
-        <f>IFERROR(VLOOKUP($B46,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B46,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D46" s="14">
-        <f>IFERROR(VLOOKUP($B46,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B46,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E46" s="15">
-        <f>IFERROR(VLOOKUP($B46,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B46,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F46" s="15">
-        <f>IFERROR(VLOOKUP($B46,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B46,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G46" s="16">
@@ -2246,12 +2394,12 @@
         <v/>
       </c>
       <c r="H46" s="17">
-        <f>IF($B46="CA","",-F46/SUM(F35:F47))</f>
+        <f>IF($C46="Produits","",-F46/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I46" s="4" t="n"/>
       <c r="J46">
-        <f>IFERROR(VLOOKUP($B46,$N$7:$S$26,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B46,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="K46">
@@ -2267,23 +2415,23 @@
       <c r="A47" s="4" t="n"/>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>SIEGE</t>
+          <t>625</t>
         </is>
       </c>
       <c r="C47" s="13">
-        <f>IFERROR(VLOOKUP($B47,$N$7:$S$26,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B47,$N$7:$S$28,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="D47" s="14">
-        <f>IFERROR(VLOOKUP($B47,$N$7:$S$26,3,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B47,$N$7:$S$28,3,FALSE),"")</f>
         <v/>
       </c>
       <c r="E47" s="15">
-        <f>IFERROR(VLOOKUP($B47,$N$7:$S$26,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B47,$N$7:$S$28,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F47" s="15">
-        <f>IFERROR(VLOOKUP($B47,$N$7:$S$26,6,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($B47,$N$7:$S$28,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G47" s="16">
@@ -2291,12 +2439,12 @@
         <v/>
       </c>
       <c r="H47" s="17">
-        <f>IF($B47="CA","",-F47/SUM(F35:F47))</f>
+        <f>IF($C47="Produits","",-F47/SUM(F37:F49))</f>
         <v/>
       </c>
       <c r="I47" s="4" t="n"/>
       <c r="J47">
-        <f>IFERROR(VLOOKUP($B47,$N$7:$S$26,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($B47,$N$7:$S$28,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="K47">
@@ -2308,41 +2456,95 @@
         <v/>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="15.5" customHeight="1">
       <c r="A48" s="4" t="n"/>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>63511</t>
+        </is>
+      </c>
+      <c r="C48" s="13">
+        <f>IFERROR(VLOOKUP($B48,$N$7:$S$28,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="14">
+        <f>IFERROR(VLOOKUP($B48,$N$7:$S$28,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="15">
+        <f>IFERROR(VLOOKUP($B48,$N$7:$S$28,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F48" s="15">
+        <f>IFERROR(VLOOKUP($B48,$N$7:$S$28,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G48" s="16">
+        <f>F48-E48</f>
+        <v/>
+      </c>
+      <c r="H48" s="17">
+        <f>IF($C48="Produits","",-F48/SUM(F37:F49))</f>
+        <v/>
+      </c>
       <c r="I48" s="4" t="n"/>
-    </row>
-    <row r="49">
+      <c r="J48">
+        <f>IFERROR(VLOOKUP($B48,$N$7:$S$28,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K48">
+        <f>-E48</f>
+        <v/>
+      </c>
+      <c r="L48">
+        <f>-F48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="15.5" customHeight="1">
       <c r="A49" s="4" t="n"/>
-      <c r="B49" s="18" t="inlineStr">
-        <is>
-          <t>Contrôle</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="n"/>
-      <c r="D49" s="18" t="inlineStr">
-        <is>
-          <t>la somme des quatorze lignes doit valoir l'EBITDA</t>
-        </is>
-      </c>
-      <c r="E49" s="20">
-        <f>SUM(E34:E47)</f>
-        <v/>
-      </c>
-      <c r="F49" s="20">
-        <f>SUM(F34:F47)</f>
-        <v/>
-      </c>
-      <c r="G49" s="19" t="n"/>
-      <c r="H49" s="19" t="n"/>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>SIEGE</t>
+        </is>
+      </c>
+      <c r="C49" s="13">
+        <f>IFERROR(VLOOKUP($B49,$N$7:$S$28,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="14">
+        <f>IFERROR(VLOOKUP($B49,$N$7:$S$28,3,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="15">
+        <f>IFERROR(VLOOKUP($B49,$N$7:$S$28,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="F49" s="15">
+        <f>IFERROR(VLOOKUP($B49,$N$7:$S$28,6,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="G49" s="16">
+        <f>F49-E49</f>
+        <v/>
+      </c>
+      <c r="H49" s="17">
+        <f>IF($C49="Produits","",-F49/SUM(F37:F49))</f>
+        <v/>
+      </c>
       <c r="I49" s="4" t="n"/>
+      <c r="J49">
+        <f>IFERROR(VLOOKUP($B49,$N$7:$S$28,4,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K49">
+        <f>-E49</f>
+        <v/>
+      </c>
+      <c r="L49">
+        <f>-F49</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n"/>
@@ -2355,123 +2557,129 @@
       <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="n"/>
     </row>
-    <row r="51" ht="20" customHeight="1">
+    <row r="51">
       <c r="A51" s="4" t="n"/>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>RAPPROCHEMENT DU CHIFFRE D'AFFAIRES  ·  gestion contre socle CRM</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>Contrôle</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="n"/>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>la somme des seize lignes doit valoir l'EBITDA</t>
+        </is>
+      </c>
+      <c r="E51" s="20">
+        <f>SUM(E34:E49)</f>
+        <v/>
+      </c>
+      <c r="F51" s="20">
+        <f>SUM(F34:F49)</f>
+        <v/>
+      </c>
+      <c r="G51" s="19" t="n"/>
+      <c r="H51" s="19" t="n"/>
       <c r="I51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n"/>
-      <c r="B52" s="21" t="inlineStr">
-        <is>
-          <t>Chiffre d'affaires en gestion  ·  706 initiaux + 7062 alternants + 708 inscription</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="22" t="n"/>
-      <c r="E52" s="23">
-        <f>$O$29</f>
-        <v/>
-      </c>
-      <c r="F52" s="23">
-        <f>$P$29</f>
-        <v/>
-      </c>
-      <c r="G52" s="22" t="n"/>
-      <c r="H52" s="22" t="n"/>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="20" customHeight="1">
       <c r="A53" s="4" t="n"/>
-      <c r="B53" s="21" t="inlineStr">
-        <is>
-          <t>Chiffre d'affaires du socle CRM  ·  effectifs × droits de scolarité</t>
-        </is>
-      </c>
-      <c r="C53" s="22" t="n"/>
-      <c r="D53" s="22" t="n"/>
-      <c r="E53" s="23">
-        <f>E34</f>
-        <v/>
-      </c>
-      <c r="F53" s="23">
-        <f>F34</f>
-        <v/>
-      </c>
-      <c r="G53" s="22" t="n"/>
-      <c r="H53" s="22" t="n"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>RAPPROCHEMENT DU CHIFFRE D'AFFAIRES  ·  comptes de produit contre socle CRM</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n"/>
-      <c r="B54" s="24" t="inlineStr">
-        <is>
-          <t>Écart</t>
-        </is>
-      </c>
-      <c r="C54" s="25" t="n"/>
-      <c r="D54" s="25" t="n"/>
-      <c r="E54" s="26">
-        <f>E52-E53</f>
-        <v/>
-      </c>
-      <c r="F54" s="26">
-        <f>F52-F53</f>
-        <v/>
-      </c>
-      <c r="G54" s="27">
-        <f>E54/E53</f>
-        <v/>
-      </c>
-      <c r="H54" s="27">
-        <f>F54/F53</f>
-        <v/>
-      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>Comptes de produit  ·  706 + 7062 + 708, somme des trois lignes ci-dessus</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="23">
+        <f>SUM(E34:E36)</f>
+        <v/>
+      </c>
+      <c r="F54" s="23">
+        <f>SUM(F34:F36)</f>
+        <v/>
+      </c>
+      <c r="G54" s="22" t="n"/>
+      <c r="H54" s="22" t="n"/>
       <c r="I54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="n"/>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
+      <c r="B55" s="21" t="inlineStr">
+        <is>
+          <t>Socle CRM  ·  effectifs × droits de scolarité, restitution de Q_D3_CA_CRM</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="23">
+        <f>SUM($T$31:$T$33)</f>
+        <v/>
+      </c>
+      <c r="F55" s="23">
+        <f>SUM($U$31:$U$33)</f>
+        <v/>
+      </c>
+      <c r="G55" s="22" t="n"/>
+      <c r="H55" s="22" t="n"/>
       <c r="I55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n"/>
-      <c r="B56" s="28" t="inlineStr">
-        <is>
-          <t>Ce rapprochement est un CONTRÔLE, pas une source. V_ALLOCATION ne lit jamais les comptes de produit : le chiffre d'affaires du modèle vient du socle CRM, quoi que disent le 706, le 7062 et le 708.</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>Écart</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="n"/>
+      <c r="D56" s="25" t="n"/>
+      <c r="E56" s="26">
+        <f>E54-E55</f>
+        <v/>
+      </c>
+      <c r="F56" s="26">
+        <f>F54-F55</f>
+        <v/>
+      </c>
+      <c r="G56" s="27">
+        <f>E56/E55</f>
+        <v/>
+      </c>
+      <c r="H56" s="27">
+        <f>F56/F55</f>
+        <v/>
+      </c>
       <c r="I56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n"/>
-      <c r="B57" s="28" t="inlineStr">
-        <is>
-          <t>Le modèle prend le CRM pour deux raisons qui ne tiennent pas à l'exactitude. Le GRAIN — 180 lignes campus × programme × année × modalité contre 105 au grain campus × compte, sans quoi aucune marge par programme n'est calculable.</t>
-        </is>
-      </c>
+      <c r="B57" s="4" t="n"/>
       <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="n"/>
@@ -2484,7 +2692,7 @@
       <c r="A58" s="4" t="n"/>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Et le PILOTAGE — le CRM donne le CA comme un produit d'inducteurs, effectifs × droits de scolarité, donc il se simule. Un montant déjà posé est un constat.</t>
+          <t>Les deux chaînes disent le même montant depuis le réalignement du 06/09. Cet écart doit rester à zéro ; s'il reparaît, c'est que le socle CRM a bougé sans que les comptes de produit suivent — FIX_CA_COMPTA_2024_2025.sql les remet d'accord.</t>
         </is>
       </c>
       <c r="C58" s="4" t="n"/>
@@ -2499,7 +2707,7 @@
       <c r="A59" s="4" t="n"/>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>Les trois exercices tombent désormais au centime. 2024 et 2025 portaient un estimé établi séparément, à ± 0,08 % près ; FIX_CA_COMPTA_2024_2025.sql les a réalignés sur le CRM, 70 lignes recalculées et pas un centime d'EBITDA déplacé.</t>
+          <t>C'est ce qui permet d'ouvrir le chiffre d'affaires en trois comptes ici : le tableau est un vrai compte d'exploitation, quinze lignes qui sont toutes de vraies écritures, plus le siège qui est une allocation et le dit.</t>
         </is>
       </c>
       <c r="C59" s="4" t="n"/>
@@ -2512,7 +2720,11 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="n"/>
-      <c r="B60" s="4" t="n"/>
+      <c r="B60" s="28" t="inlineStr">
+        <is>
+          <t>Le modèle continue de piloter par le CRM, et pour deux raisons qui ne tiennent pas à l'exactitude. Le GRAIN — 180 lignes campus × programme × année × modalité contre 105 au grain campus × compte, sans quoi aucune marge par programme n'est calculable.</t>
+        </is>
+      </c>
       <c r="C60" s="4" t="n"/>
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="n"/>
@@ -2523,7 +2735,11 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="n"/>
-      <c r="B61" s="4" t="n"/>
+      <c r="B61" s="28" t="inlineStr">
+        <is>
+          <t>Et le PILOTAGE — le CRM donne le CA comme un produit d'inducteurs, effectifs × droits de scolarité, donc il se simule. Un montant déjà posé est un constat. DRILL3 ouvre cette chaîne-là.</t>
+        </is>
+      </c>
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="n"/>
@@ -2565,10 +2781,32 @@
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="n"/>
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="n"/>
+      <c r="G65" s="4" t="n"/>
+      <c r="H65" s="4" t="n"/>
+      <c r="I65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n"/>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B34:H47">
+  <conditionalFormatting sqref="B34:H49">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$B34="CA"</formula>
+      <formula>$C34="Produits"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>$B34="SIEGE"</formula>
@@ -2577,7 +2815,7 @@
       <formula>$B34&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G34:G47">
+  <conditionalFormatting sqref="G34:G49">
     <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -2585,7 +2823,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H47">
+  <conditionalFormatting sqref="H34:H49">
     <cfRule type="dataBar" priority="6">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>

--- a/eduservices/DRILL2_EXCEL.xlsx
+++ b/eduservices/DRILL2_EXCEL.xlsx
@@ -819,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U66"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -840,8 +840,6 @@
     <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
     <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
     <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
-    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
-    <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="8" customHeight="1">
@@ -1646,30 +1644,10 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>Poste court</t>
+          <t>Montant 2025</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
-        <is>
-          <t>Unite comptee</t>
-        </is>
-      </c>
-      <c r="R30" s="7" t="inlineStr">
-        <is>
-          <t>Volume 2025</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>Volume 2026</t>
-        </is>
-      </c>
-      <c r="T30" s="7" t="inlineStr">
-        <is>
-          <t>Montant 2025</t>
-        </is>
-      </c>
-      <c r="U30" s="7" t="inlineStr">
         <is>
           <t>Montant 2026</t>
         </is>
@@ -1695,26 +1673,10 @@
           <t>Scolarité des étudiants en initial</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Scolarité initial</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Effectifs</t>
-        </is>
-      </c>
-      <c r="R31" t="n">
-        <v>400</v>
-      </c>
-      <c r="S31" t="n">
-        <v>424</v>
-      </c>
-      <c r="T31" t="n">
+      <c r="P31" t="n">
         <v>3120000</v>
       </c>
-      <c r="U31" t="n">
+      <c r="Q31" t="n">
         <v>3306675</v>
       </c>
     </row>
@@ -1746,26 +1708,10 @@
           <t>Scolarité des alternants</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Scolarité alternance</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Effectifs</t>
-        </is>
-      </c>
-      <c r="R32" t="n">
-        <v>2533</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2690</v>
-      </c>
-      <c r="T32" t="n">
+      <c r="P32" t="n">
         <v>18534460</v>
       </c>
-      <c r="U32" t="n">
+      <c r="Q32" t="n">
         <v>19681700</v>
       </c>
     </row>
@@ -1827,26 +1773,10 @@
           <t>Frais d'inscription</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Frais d'inscription</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Nouveaux inscrits</t>
-        </is>
-      </c>
-      <c r="R33" t="n">
-        <v>1159</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1229</v>
-      </c>
-      <c r="T33" t="n">
+      <c r="P33" t="n">
         <v>104310</v>
       </c>
-      <c r="U33" t="n">
+      <c r="Q33" t="n">
         <v>110610</v>
       </c>
     </row>
@@ -2633,17 +2563,17 @@
       <c r="A55" s="4" t="n"/>
       <c r="B55" s="21" t="inlineStr">
         <is>
-          <t>Socle CRM  ·  effectifs × droits de scolarité, restitution de Q_D3_CA_CRM</t>
+          <t>Socle CRM  ·  effectifs × droits de scolarité, restitution de Q_D2_CA_CRM</t>
         </is>
       </c>
       <c r="C55" s="22" t="n"/>
       <c r="D55" s="22" t="n"/>
       <c r="E55" s="23">
-        <f>SUM($T$31:$T$33)</f>
+        <f>SUM($P$31:$P$33)</f>
         <v/>
       </c>
       <c r="F55" s="23">
-        <f>SUM($U$31:$U$33)</f>
+        <f>SUM($Q$31:$Q$33)</f>
         <v/>
       </c>
       <c r="G55" s="22" t="n"/>
@@ -2737,7 +2667,7 @@
       <c r="A61" s="4" t="n"/>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>Et le PILOTAGE — le CRM donne le CA comme un produit d'inducteurs, effectifs × droits de scolarité, donc il se simule. Un montant déjà posé est un constat. DRILL3 ouvre cette chaîne-là.</t>
+          <t>Et le PILOTAGE — le CRM donne le CA comme un produit d'inducteurs, effectifs × droits de scolarité, donc il se simule. Un montant déjà posé est un constat.</t>
         </is>
       </c>
       <c r="C61" s="4" t="n"/>
